--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/09,26/10,09,26 ПОКОМ ЗПФ/дв 10,09,26 бррсч пок зпф.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/09,26/10,09,26 ПОКОМ ЗПФ/дв 10,09,26 бррсч пок зпф.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\09,26\10,09,26 ПОКОМ ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD287975-7105-4170-8BDD-194EB75B5032}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1ABCED1-C428-4D27-80C8-0D170C94D6EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,15 +21,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AM$73</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029" refMode="R1C1"/>
 </workbook>
 </file>
 
@@ -763,7 +755,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Sheet"/>
@@ -1092,7 +1084,8 @@
     <col min="36" max="36" width="6.5703125" customWidth="1"/>
     <col min="37" max="38" width="5" customWidth="1"/>
     <col min="39" max="39" width="6" style="12" customWidth="1"/>
-    <col min="40" max="49" width="3" customWidth="1"/>
+    <col min="40" max="40" width="9.42578125" customWidth="1"/>
+    <col min="41" max="49" width="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:49" x14ac:dyDescent="0.25">
@@ -1524,7 +1517,10 @@
         <f>SUM(AM6:AM500)</f>
         <v>29.996031746031743</v>
       </c>
-      <c r="AN5" s="1"/>
+      <c r="AN5" s="4">
+        <f>SUM(AN6:AN500)</f>
+        <v>1341.6039999999998</v>
+      </c>
       <c r="AO5" s="1"/>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="1"/>
@@ -1627,7 +1623,10 @@
       <c r="AK6" s="14"/>
       <c r="AL6" s="14"/>
       <c r="AM6" s="17"/>
-      <c r="AN6" s="1"/>
+      <c r="AN6" s="1">
+        <f>P6*G6</f>
+        <v>0</v>
+      </c>
       <c r="AO6" s="1"/>
       <c r="AP6" s="1"/>
       <c r="AQ6" s="1"/>
@@ -1730,7 +1729,10 @@
       <c r="AK7" s="14"/>
       <c r="AL7" s="14"/>
       <c r="AM7" s="17"/>
-      <c r="AN7" s="1"/>
+      <c r="AN7" s="1">
+        <f t="shared" ref="AN7:AN70" si="6">P7*G7</f>
+        <v>0</v>
+      </c>
       <c r="AO7" s="1"/>
       <c r="AP7" s="1"/>
       <c r="AQ7" s="1"/>
@@ -1827,7 +1829,10 @@
       <c r="AK8" s="14"/>
       <c r="AL8" s="14"/>
       <c r="AM8" s="17"/>
-      <c r="AN8" s="1"/>
+      <c r="AN8" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AO8" s="1"/>
       <c r="AP8" s="1"/>
       <c r="AQ8" s="1"/>
@@ -1953,7 +1958,10 @@
         <f>AI9/AL9</f>
         <v>0</v>
       </c>
-      <c r="AN9" s="1"/>
+      <c r="AN9" s="1">
+        <f t="shared" si="6"/>
+        <v>0.88</v>
+      </c>
       <c r="AO9" s="1"/>
       <c r="AP9" s="1"/>
       <c r="AQ9" s="1"/>
@@ -2082,7 +2090,10 @@
         <f>AI10/AL10</f>
         <v>0.4</v>
       </c>
-      <c r="AN10" s="1"/>
+      <c r="AN10" s="1">
+        <f t="shared" si="6"/>
+        <v>11.88</v>
+      </c>
       <c r="AO10" s="1"/>
       <c r="AP10" s="1"/>
       <c r="AQ10" s="1"/>
@@ -2185,7 +2196,10 @@
       <c r="AK11" s="14"/>
       <c r="AL11" s="14"/>
       <c r="AM11" s="17"/>
-      <c r="AN11" s="1"/>
+      <c r="AN11" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AO11" s="1"/>
       <c r="AP11" s="1"/>
       <c r="AQ11" s="1"/>
@@ -2314,7 +2328,10 @@
         <f>AI12/AL12</f>
         <v>0.9</v>
       </c>
-      <c r="AN12" s="1"/>
+      <c r="AN12" s="1">
+        <f t="shared" si="6"/>
+        <v>21.056000000000004</v>
+      </c>
       <c r="AO12" s="1"/>
       <c r="AP12" s="1"/>
       <c r="AQ12" s="1"/>
@@ -2443,7 +2460,10 @@
         <f>AI13/AL13</f>
         <v>0.6</v>
       </c>
-      <c r="AN13" s="1"/>
+      <c r="AN13" s="1">
+        <f t="shared" si="6"/>
+        <v>19.391999999999999</v>
+      </c>
       <c r="AO13" s="1"/>
       <c r="AP13" s="1"/>
       <c r="AQ13" s="1"/>
@@ -2546,7 +2566,10 @@
       <c r="AK14" s="14"/>
       <c r="AL14" s="14"/>
       <c r="AM14" s="17"/>
-      <c r="AN14" s="1"/>
+      <c r="AN14" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AO14" s="1"/>
       <c r="AP14" s="1"/>
       <c r="AQ14" s="1"/>
@@ -2606,7 +2629,7 @@
         <v>771.60000000000014</v>
       </c>
       <c r="R15" s="5">
-        <f t="shared" ref="R15:R16" si="6">14*P15-F15</f>
+        <f t="shared" ref="R15" si="7">14*P15-F15</f>
         <v>771.60000000000014</v>
       </c>
       <c r="S15" s="5">
@@ -2677,7 +2700,10 @@
         <f>AI15/AL15</f>
         <v>1</v>
       </c>
-      <c r="AN15" s="1"/>
+      <c r="AN15" s="1">
+        <f t="shared" si="6"/>
+        <v>20.496000000000002</v>
+      </c>
       <c r="AO15" s="1"/>
       <c r="AP15" s="1"/>
       <c r="AQ15" s="1"/>
@@ -2806,7 +2832,10 @@
         <f>AI16/AL16</f>
         <v>0.4</v>
       </c>
-      <c r="AN16" s="1"/>
+      <c r="AN16" s="1">
+        <f t="shared" si="6"/>
+        <v>10.655999999999999</v>
+      </c>
       <c r="AO16" s="1"/>
       <c r="AP16" s="1"/>
       <c r="AQ16" s="1"/>
@@ -2909,7 +2938,10 @@
       <c r="AK17" s="14"/>
       <c r="AL17" s="14"/>
       <c r="AM17" s="17"/>
-      <c r="AN17" s="1"/>
+      <c r="AN17" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AO17" s="1"/>
       <c r="AP17" s="1"/>
       <c r="AQ17" s="1"/>
@@ -2969,7 +3001,7 @@
         <v>583.60000000000014</v>
       </c>
       <c r="R18" s="5">
-        <f t="shared" ref="R18:R20" si="7">IF(14*P18-F18+P18*$R$1&lt;0,0,14*P18-F18+P18*$R$1)</f>
+        <f t="shared" ref="R18:R20" si="8">IF(14*P18-F18+P18*$R$1&lt;0,0,14*P18-F18+P18*$R$1)</f>
         <v>714.88000000000011</v>
       </c>
       <c r="S18" s="5">
@@ -3040,7 +3072,10 @@
         <f>AI18/AL18</f>
         <v>0.8</v>
       </c>
-      <c r="AN18" s="1"/>
+      <c r="AN18" s="1">
+        <f t="shared" si="6"/>
+        <v>26.256</v>
+      </c>
       <c r="AO18" s="1"/>
       <c r="AP18" s="1"/>
       <c r="AQ18" s="1"/>
@@ -3100,7 +3135,7 @@
         <v>150</v>
       </c>
       <c r="R19" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>175.2</v>
       </c>
       <c r="S19" s="5">
@@ -3171,7 +3206,10 @@
         <f>AI19/AL19</f>
         <v>0.4</v>
       </c>
-      <c r="AN19" s="1"/>
+      <c r="AN19" s="1">
+        <f t="shared" si="6"/>
+        <v>10.08</v>
+      </c>
       <c r="AO19" s="1"/>
       <c r="AP19" s="1"/>
       <c r="AQ19" s="1"/>
@@ -3227,7 +3265,7 @@
       </c>
       <c r="Q20" s="5"/>
       <c r="R20" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>76.8</v>
       </c>
       <c r="S20" s="5">
@@ -3298,7 +3336,10 @@
         <f>AI20/AL20</f>
         <v>0</v>
       </c>
-      <c r="AN20" s="1"/>
+      <c r="AN20" s="1">
+        <f t="shared" si="6"/>
+        <v>3.06</v>
+      </c>
       <c r="AO20" s="1"/>
       <c r="AP20" s="1"/>
       <c r="AQ20" s="1"/>
@@ -3426,7 +3467,10 @@
         <f>AI21/AL21</f>
         <v>0</v>
       </c>
-      <c r="AN21" s="1"/>
+      <c r="AN21" s="1">
+        <f t="shared" si="6"/>
+        <v>4.68</v>
+      </c>
       <c r="AO21" s="1"/>
       <c r="AP21" s="1"/>
       <c r="AQ21" s="1"/>
@@ -3525,7 +3569,10 @@
       <c r="AK22" s="14"/>
       <c r="AL22" s="14"/>
       <c r="AM22" s="17"/>
-      <c r="AN22" s="1"/>
+      <c r="AN22" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AO22" s="1"/>
       <c r="AP22" s="1"/>
       <c r="AQ22" s="1"/>
@@ -3649,7 +3696,10 @@
         <f>AI23/AL23</f>
         <v>0</v>
       </c>
-      <c r="AN23" s="1"/>
+      <c r="AN23" s="1">
+        <f t="shared" si="6"/>
+        <v>2.2800000000000002</v>
+      </c>
       <c r="AO23" s="1"/>
       <c r="AP23" s="1"/>
       <c r="AQ23" s="1"/>
@@ -3778,7 +3828,10 @@
         <f>AI24/AL24</f>
         <v>0.8</v>
       </c>
-      <c r="AN24" s="1"/>
+      <c r="AN24" s="1">
+        <f t="shared" si="6"/>
+        <v>13.600000000000001</v>
+      </c>
       <c r="AO24" s="1"/>
       <c r="AP24" s="1"/>
       <c r="AQ24" s="1"/>
@@ -3907,7 +3960,10 @@
         <f>AI25/AL25</f>
         <v>0.2</v>
       </c>
-      <c r="AN25" s="1"/>
+      <c r="AN25" s="1">
+        <f t="shared" si="6"/>
+        <v>8.08</v>
+      </c>
       <c r="AO25" s="1"/>
       <c r="AP25" s="1"/>
       <c r="AQ25" s="1"/>
@@ -3965,7 +4021,7 @@
         <v>39.599999999999994</v>
       </c>
       <c r="R26" s="5">
-        <f t="shared" ref="R24:R26" si="8">14*P26-F26</f>
+        <f t="shared" ref="R26" si="9">14*P26-F26</f>
         <v>39.599999999999994</v>
       </c>
       <c r="S26" s="5">
@@ -4036,7 +4092,10 @@
         <f>AI26/AL26</f>
         <v>0.1111111111111111</v>
       </c>
-      <c r="AN26" s="1"/>
+      <c r="AN26" s="1">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
       <c r="AO26" s="1"/>
       <c r="AP26" s="1"/>
       <c r="AQ26" s="1"/>
@@ -4141,7 +4200,10 @@
       <c r="AK27" s="14"/>
       <c r="AL27" s="14"/>
       <c r="AM27" s="17"/>
-      <c r="AN27" s="1"/>
+      <c r="AN27" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AO27" s="1"/>
       <c r="AP27" s="1"/>
       <c r="AQ27" s="1"/>
@@ -4199,11 +4261,11 @@
         <v>30.600000000000009</v>
       </c>
       <c r="R28" s="5">
-        <f t="shared" ref="R28:R73" si="9">14*P28-F28</f>
+        <f t="shared" ref="R28:R63" si="10">14*P28-F28</f>
         <v>30.600000000000009</v>
       </c>
       <c r="S28" s="5">
-        <f t="shared" ref="S28:S73" si="10">AH28*AI28</f>
+        <f t="shared" ref="S28:S73" si="11">AH28*AI28</f>
         <v>42</v>
       </c>
       <c r="T28" s="1">
@@ -4246,18 +4308,18 @@
       </c>
       <c r="AF28" s="1"/>
       <c r="AG28" s="1">
-        <f t="shared" ref="AG28:AG73" si="11">G28*R28</f>
+        <f t="shared" ref="AG28:AG73" si="12">G28*R28</f>
         <v>30.600000000000009</v>
       </c>
       <c r="AH28" s="7">
         <v>3</v>
       </c>
       <c r="AI28" s="9">
-        <f t="shared" ref="AI28:AI73" si="12">MROUND(R28, AH28*AK28)/AH28</f>
+        <f t="shared" ref="AI28:AI73" si="13">MROUND(R28, AH28*AK28)/AH28</f>
         <v>14</v>
       </c>
       <c r="AJ28" s="1">
-        <f t="shared" ref="AJ28:AJ73" si="13">AI28*AH28*G28</f>
+        <f t="shared" ref="AJ28:AJ73" si="14">AI28*AH28*G28</f>
         <v>42</v>
       </c>
       <c r="AK28" s="1">
@@ -4267,10 +4329,13 @@
         <v>126</v>
       </c>
       <c r="AM28" s="9">
-        <f t="shared" ref="AM28:AM73" si="14">AI28/AL28</f>
+        <f t="shared" ref="AM28:AM73" si="15">AI28/AL28</f>
         <v>0.1111111111111111</v>
       </c>
-      <c r="AN28" s="1"/>
+      <c r="AN28" s="1">
+        <f t="shared" si="6"/>
+        <v>8.4</v>
+      </c>
       <c r="AO28" s="1"/>
       <c r="AP28" s="1"/>
       <c r="AQ28" s="1"/>
@@ -4334,7 +4399,7 @@
         <v>831.2800000000002</v>
       </c>
       <c r="S29" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>840</v>
       </c>
       <c r="T29" s="1">
@@ -4377,18 +4442,18 @@
       </c>
       <c r="AF29" s="1"/>
       <c r="AG29" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>207.82000000000005</v>
       </c>
       <c r="AH29" s="7">
         <v>6</v>
       </c>
       <c r="AI29" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>140</v>
       </c>
       <c r="AJ29" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>210</v>
       </c>
       <c r="AK29" s="1">
@@ -4398,10 +4463,13 @@
         <v>140</v>
       </c>
       <c r="AM29" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="AN29" s="1"/>
+      <c r="AN29" s="1">
+        <f t="shared" si="6"/>
+        <v>26.6</v>
+      </c>
       <c r="AO29" s="1"/>
       <c r="AP29" s="1"/>
       <c r="AQ29" s="1"/>
@@ -4463,7 +4531,7 @@
         <v>479</v>
       </c>
       <c r="S30" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>504</v>
       </c>
       <c r="T30" s="1">
@@ -4506,18 +4574,18 @@
       </c>
       <c r="AF30" s="1"/>
       <c r="AG30" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>119.75</v>
       </c>
       <c r="AH30" s="7">
         <v>6</v>
       </c>
       <c r="AI30" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>84</v>
       </c>
       <c r="AJ30" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>126</v>
       </c>
       <c r="AK30" s="1">
@@ -4527,10 +4595,13 @@
         <v>140</v>
       </c>
       <c r="AM30" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.6</v>
       </c>
-      <c r="AN30" s="1"/>
+      <c r="AN30" s="1">
+        <f t="shared" si="6"/>
+        <v>12.05</v>
+      </c>
       <c r="AO30" s="1"/>
       <c r="AP30" s="1"/>
       <c r="AQ30" s="1"/>
@@ -4590,7 +4661,7 @@
         <v>29.279999999999962</v>
       </c>
       <c r="S31" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="T31" s="1">
@@ -4633,20 +4704,20 @@
       </c>
       <c r="AF31" s="1"/>
       <c r="AG31" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>29.279999999999962</v>
       </c>
       <c r="AH31" s="7">
         <v>6</v>
       </c>
       <c r="AI31" s="9">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AJ31" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
+      <c r="AJ31" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AK31" s="1">
         <v>12</v>
       </c>
@@ -4654,10 +4725,13 @@
         <v>84</v>
       </c>
       <c r="AM31" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AN31" s="1"/>
+      <c r="AN31" s="1">
+        <f t="shared" si="6"/>
+        <v>26.4</v>
+      </c>
       <c r="AO31" s="1"/>
       <c r="AP31" s="1"/>
       <c r="AQ31" s="1"/>
@@ -4715,11 +4789,11 @@
         <v>139.20000000000002</v>
       </c>
       <c r="R32" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>139.20000000000002</v>
       </c>
       <c r="S32" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>168</v>
       </c>
       <c r="T32" s="1">
@@ -4762,18 +4836,18 @@
       </c>
       <c r="AF32" s="1"/>
       <c r="AG32" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>32.016000000000005</v>
       </c>
       <c r="AH32" s="7">
         <v>12</v>
       </c>
       <c r="AI32" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>14</v>
       </c>
       <c r="AJ32" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>38.64</v>
       </c>
       <c r="AK32" s="1">
@@ -4783,10 +4857,13 @@
         <v>70</v>
       </c>
       <c r="AM32" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.2</v>
       </c>
-      <c r="AN32" s="1"/>
+      <c r="AN32" s="1">
+        <f t="shared" si="6"/>
+        <v>4.0940000000000003</v>
+      </c>
       <c r="AO32" s="1"/>
       <c r="AP32" s="1"/>
       <c r="AQ32" s="1"/>
@@ -4848,7 +4925,7 @@
         <v>490.08000000000015</v>
       </c>
       <c r="S33" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>504</v>
       </c>
       <c r="T33" s="1">
@@ -4891,18 +4968,18 @@
       </c>
       <c r="AF33" s="1"/>
       <c r="AG33" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>122.52000000000004</v>
       </c>
       <c r="AH33" s="7">
         <v>12</v>
       </c>
       <c r="AI33" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>42</v>
       </c>
       <c r="AJ33" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>126</v>
       </c>
       <c r="AK33" s="1">
@@ -4912,10 +4989,13 @@
         <v>70</v>
       </c>
       <c r="AM33" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.6</v>
       </c>
-      <c r="AN33" s="1"/>
+      <c r="AN33" s="1">
+        <f t="shared" si="6"/>
+        <v>20.100000000000001</v>
+      </c>
       <c r="AO33" s="1"/>
       <c r="AP33" s="1"/>
       <c r="AQ33" s="1"/>
@@ -4973,11 +5053,11 @@
         <v>733</v>
       </c>
       <c r="R34" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>733</v>
       </c>
       <c r="S34" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>672</v>
       </c>
       <c r="T34" s="1">
@@ -5020,18 +5100,18 @@
       </c>
       <c r="AF34" s="1"/>
       <c r="AG34" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>183.25</v>
       </c>
       <c r="AH34" s="7">
         <v>12</v>
       </c>
       <c r="AI34" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>56</v>
       </c>
       <c r="AJ34" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>168</v>
       </c>
       <c r="AK34" s="1">
@@ -5041,10 +5121,13 @@
         <v>70</v>
       </c>
       <c r="AM34" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.8</v>
       </c>
-      <c r="AN34" s="1"/>
+      <c r="AN34" s="1">
+        <f t="shared" si="6"/>
+        <v>18.75</v>
+      </c>
       <c r="AO34" s="1"/>
       <c r="AP34" s="1"/>
       <c r="AQ34" s="1"/>
@@ -5102,11 +5185,11 @@
         <v>387.6</v>
       </c>
       <c r="R35" s="5">
-        <f t="shared" ref="R35:R36" si="15">IF(14*P35-F35+P35*$R$1&lt;0,0,14*P35-F35+P35*$R$1)</f>
+        <f t="shared" ref="R35:R36" si="16">IF(14*P35-F35+P35*$R$1&lt;0,0,14*P35-F35+P35*$R$1)</f>
         <v>443.28000000000003</v>
       </c>
       <c r="S35" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>504</v>
       </c>
       <c r="T35" s="1">
@@ -5149,18 +5232,18 @@
       </c>
       <c r="AF35" s="1"/>
       <c r="AG35" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>110.82000000000001</v>
       </c>
       <c r="AH35" s="7">
         <v>12</v>
       </c>
       <c r="AI35" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>42</v>
       </c>
       <c r="AJ35" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>126</v>
       </c>
       <c r="AK35" s="1">
@@ -5170,10 +5253,13 @@
         <v>70</v>
       </c>
       <c r="AM35" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.6</v>
       </c>
-      <c r="AN35" s="1"/>
+      <c r="AN35" s="1">
+        <f t="shared" si="6"/>
+        <v>11.6</v>
+      </c>
       <c r="AO35" s="1"/>
       <c r="AP35" s="1"/>
       <c r="AQ35" s="1"/>
@@ -5231,11 +5317,11 @@
         <v>251.40000000000003</v>
       </c>
       <c r="R36" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>288.12</v>
       </c>
       <c r="S36" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>336</v>
       </c>
       <c r="T36" s="1">
@@ -5278,18 +5364,18 @@
       </c>
       <c r="AF36" s="1"/>
       <c r="AG36" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>72.03</v>
       </c>
       <c r="AH36" s="7">
         <v>12</v>
       </c>
       <c r="AI36" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>28</v>
       </c>
       <c r="AJ36" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>84</v>
       </c>
       <c r="AK36" s="1">
@@ -5299,10 +5385,13 @@
         <v>70</v>
       </c>
       <c r="AM36" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.4</v>
       </c>
-      <c r="AN36" s="1"/>
+      <c r="AN36" s="1">
+        <f t="shared" si="6"/>
+        <v>7.65</v>
+      </c>
       <c r="AO36" s="1"/>
       <c r="AP36" s="1"/>
       <c r="AQ36" s="1"/>
@@ -5364,7 +5453,7 @@
         <v>342</v>
       </c>
       <c r="S37" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>384</v>
       </c>
       <c r="T37" s="1">
@@ -5407,18 +5496,18 @@
       </c>
       <c r="AF37" s="1"/>
       <c r="AG37" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>239.39999999999998</v>
       </c>
       <c r="AH37" s="7">
         <v>8</v>
       </c>
       <c r="AI37" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>48</v>
       </c>
       <c r="AJ37" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>268.79999999999995</v>
       </c>
       <c r="AK37" s="1">
@@ -5428,10 +5517,13 @@
         <v>84</v>
       </c>
       <c r="AM37" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.5714285714285714</v>
       </c>
-      <c r="AN37" s="1"/>
+      <c r="AN37" s="1">
+        <f t="shared" si="6"/>
+        <v>23.099999999999998</v>
+      </c>
       <c r="AO37" s="1"/>
       <c r="AP37" s="1"/>
       <c r="AQ37" s="1"/>
@@ -5475,14 +5567,14 @@
         <v>132</v>
       </c>
       <c r="L38" s="1">
-        <f t="shared" ref="L38:L69" si="16">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="17">E38-K38</f>
         <v>-39</v>
       </c>
       <c r="M38" s="1"/>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
       <c r="P38" s="1">
-        <f t="shared" ref="P38:P73" si="17">E38/5</f>
+        <f t="shared" ref="P38:P73" si="18">E38/5</f>
         <v>18.600000000000001</v>
       </c>
       <c r="Q38" s="5">
@@ -5493,15 +5585,15 @@
         <v>192</v>
       </c>
       <c r="S38" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>192</v>
       </c>
       <c r="T38" s="1">
-        <f t="shared" ref="T38:T69" si="18">(F38+S38)/P38</f>
+        <f t="shared" ref="T38:T69" si="19">(F38+S38)/P38</f>
         <v>10</v>
       </c>
       <c r="U38" s="1">
-        <f t="shared" ref="U38:U73" si="19">F38/P38</f>
+        <f t="shared" ref="U38:U73" si="20">F38/P38</f>
         <v>-0.32258064516129031</v>
       </c>
       <c r="V38" s="1">
@@ -5536,18 +5628,18 @@
       </c>
       <c r="AF38" s="1"/>
       <c r="AG38" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>134.39999999999998</v>
       </c>
       <c r="AH38" s="7">
         <v>8</v>
       </c>
       <c r="AI38" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>24</v>
       </c>
       <c r="AJ38" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>134.39999999999998</v>
       </c>
       <c r="AK38" s="1">
@@ -5557,10 +5649,13 @@
         <v>84</v>
       </c>
       <c r="AM38" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.2857142857142857</v>
       </c>
-      <c r="AN38" s="1"/>
+      <c r="AN38" s="1">
+        <f t="shared" si="6"/>
+        <v>13.02</v>
+      </c>
       <c r="AO38" s="1"/>
       <c r="AP38" s="1"/>
       <c r="AQ38" s="1"/>
@@ -5600,14 +5695,14 @@
         <v>72</v>
       </c>
       <c r="L39" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-72</v>
       </c>
       <c r="M39" s="1"/>
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
       <c r="P39" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Q39" s="21">
@@ -5617,17 +5712,17 @@
         <v>0</v>
       </c>
       <c r="S39" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="T39" s="1" t="e">
-        <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U39" s="1" t="e">
         <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="U39" s="1" t="e">
+        <f t="shared" si="20"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="V39" s="1">
         <v>1</v>
       </c>
@@ -5662,20 +5757,20 @@
         <v>74</v>
       </c>
       <c r="AG39" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AH39" s="7">
         <v>8</v>
       </c>
       <c r="AI39" s="9">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AJ39" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
+      <c r="AJ39" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AK39" s="1">
         <v>12</v>
       </c>
@@ -5683,10 +5778,13 @@
         <v>84</v>
       </c>
       <c r="AM39" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AN39" s="1"/>
+      <c r="AN39" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AO39" s="1"/>
       <c r="AP39" s="1"/>
       <c r="AQ39" s="1"/>
@@ -5730,14 +5828,14 @@
         <v>303</v>
       </c>
       <c r="L40" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-16</v>
       </c>
       <c r="M40" s="1"/>
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
       <c r="P40" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>57.4</v>
       </c>
       <c r="Q40" s="5">
@@ -5748,15 +5846,15 @@
         <v>424.48</v>
       </c>
       <c r="S40" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>480</v>
       </c>
       <c r="T40" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>16.167247386759581</v>
       </c>
       <c r="U40" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>7.8048780487804876</v>
       </c>
       <c r="V40" s="1">
@@ -5791,18 +5889,18 @@
       </c>
       <c r="AF40" s="1"/>
       <c r="AG40" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>297.13599999999997</v>
       </c>
       <c r="AH40" s="7">
         <v>10</v>
       </c>
       <c r="AI40" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>48</v>
       </c>
       <c r="AJ40" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>336</v>
       </c>
       <c r="AK40" s="1">
@@ -5812,10 +5910,13 @@
         <v>84</v>
       </c>
       <c r="AM40" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.5714285714285714</v>
       </c>
-      <c r="AN40" s="1"/>
+      <c r="AN40" s="1">
+        <f t="shared" si="6"/>
+        <v>40.18</v>
+      </c>
       <c r="AO40" s="1"/>
       <c r="AP40" s="1"/>
       <c r="AQ40" s="1"/>
@@ -5859,14 +5960,14 @@
         <v>237</v>
       </c>
       <c r="L41" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2</v>
       </c>
       <c r="M41" s="1"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
       <c r="P41" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>47.8</v>
       </c>
       <c r="Q41" s="5">
@@ -5877,15 +5978,15 @@
         <v>465.4</v>
       </c>
       <c r="S41" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>480</v>
       </c>
       <c r="T41" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>13.305439330543933</v>
       </c>
       <c r="U41" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>3.2635983263598329</v>
       </c>
       <c r="V41" s="1">
@@ -5920,18 +6021,18 @@
       </c>
       <c r="AF41" s="1"/>
       <c r="AG41" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>325.77999999999997</v>
       </c>
       <c r="AH41" s="7">
         <v>10</v>
       </c>
       <c r="AI41" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>48</v>
       </c>
       <c r="AJ41" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>336</v>
       </c>
       <c r="AK41" s="1">
@@ -5941,10 +6042,13 @@
         <v>84</v>
       </c>
       <c r="AM41" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.5714285714285714</v>
       </c>
-      <c r="AN41" s="1"/>
+      <c r="AN41" s="1">
+        <f t="shared" si="6"/>
+        <v>33.459999999999994</v>
+      </c>
       <c r="AO41" s="1"/>
       <c r="AP41" s="1"/>
       <c r="AQ41" s="1"/>
@@ -5988,14 +6092,14 @@
         <v>446</v>
       </c>
       <c r="L42" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-18</v>
       </c>
       <c r="M42" s="1"/>
       <c r="N42" s="1"/>
       <c r="O42" s="1"/>
       <c r="P42" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>85.6</v>
       </c>
       <c r="Q42" s="5">
@@ -6006,15 +6110,15 @@
         <v>817.59999999999991</v>
       </c>
       <c r="S42" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>840</v>
       </c>
       <c r="T42" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>11.261682242990656</v>
       </c>
       <c r="U42" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1.4485981308411215</v>
       </c>
       <c r="V42" s="1">
@@ -6049,18 +6153,18 @@
       </c>
       <c r="AF42" s="1"/>
       <c r="AG42" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>572.31999999999994</v>
       </c>
       <c r="AH42" s="7">
         <v>10</v>
       </c>
       <c r="AI42" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>84</v>
       </c>
       <c r="AJ42" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>588</v>
       </c>
       <c r="AK42" s="1">
@@ -6070,10 +6174,13 @@
         <v>84</v>
       </c>
       <c r="AM42" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="AN42" s="1"/>
+      <c r="AN42" s="1">
+        <f t="shared" si="6"/>
+        <v>59.919999999999995</v>
+      </c>
       <c r="AO42" s="1"/>
       <c r="AP42" s="1"/>
       <c r="AQ42" s="1"/>
@@ -6117,33 +6224,33 @@
         <v>140</v>
       </c>
       <c r="L43" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-19</v>
       </c>
       <c r="M43" s="1"/>
       <c r="N43" s="1"/>
       <c r="O43" s="1"/>
       <c r="P43" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>24.2</v>
       </c>
       <c r="Q43" s="5">
         <v>235.2</v>
       </c>
       <c r="R43" s="5">
-        <f t="shared" ref="R43:R44" si="20">11*P43-F43</f>
+        <f t="shared" ref="R43:R44" si="21">11*P43-F43</f>
         <v>235.2</v>
       </c>
       <c r="S43" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>240</v>
       </c>
       <c r="T43" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>11.198347107438018</v>
       </c>
       <c r="U43" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1.28099173553719</v>
       </c>
       <c r="V43" s="1">
@@ -6178,18 +6285,18 @@
       </c>
       <c r="AF43" s="1"/>
       <c r="AG43" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>164.64</v>
       </c>
       <c r="AH43" s="7">
         <v>10</v>
       </c>
       <c r="AI43" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>24</v>
       </c>
       <c r="AJ43" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>168</v>
       </c>
       <c r="AK43" s="1">
@@ -6199,10 +6306,13 @@
         <v>84</v>
       </c>
       <c r="AM43" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.2857142857142857</v>
       </c>
-      <c r="AN43" s="1"/>
+      <c r="AN43" s="1">
+        <f t="shared" si="6"/>
+        <v>16.939999999999998</v>
+      </c>
       <c r="AO43" s="1"/>
       <c r="AP43" s="1"/>
       <c r="AQ43" s="1"/>
@@ -6246,33 +6356,33 @@
         <v>840</v>
       </c>
       <c r="L44" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-15</v>
       </c>
       <c r="M44" s="1"/>
       <c r="N44" s="1"/>
       <c r="O44" s="1"/>
       <c r="P44" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>165</v>
       </c>
       <c r="Q44" s="5">
         <v>1725</v>
       </c>
       <c r="R44" s="5">
+        <f t="shared" si="21"/>
+        <v>1725</v>
+      </c>
+      <c r="S44" s="5">
+        <f t="shared" si="11"/>
+        <v>1740</v>
+      </c>
+      <c r="T44" s="1">
+        <f t="shared" si="19"/>
+        <v>11.090909090909092</v>
+      </c>
+      <c r="U44" s="1">
         <f t="shared" si="20"/>
-        <v>1725</v>
-      </c>
-      <c r="S44" s="5">
-        <f t="shared" si="10"/>
-        <v>1740</v>
-      </c>
-      <c r="T44" s="1">
-        <f t="shared" si="18"/>
-        <v>11.090909090909092</v>
-      </c>
-      <c r="U44" s="1">
-        <f t="shared" si="19"/>
         <v>0.54545454545454541</v>
       </c>
       <c r="V44" s="1">
@@ -6307,18 +6417,18 @@
       </c>
       <c r="AF44" s="1"/>
       <c r="AG44" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1725</v>
       </c>
       <c r="AH44" s="7">
         <v>5</v>
       </c>
       <c r="AI44" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>348</v>
       </c>
       <c r="AJ44" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1740</v>
       </c>
       <c r="AK44" s="1">
@@ -6328,10 +6438,13 @@
         <v>144</v>
       </c>
       <c r="AM44" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>2.4166666666666665</v>
       </c>
-      <c r="AN44" s="1"/>
+      <c r="AN44" s="1">
+        <f t="shared" si="6"/>
+        <v>165</v>
+      </c>
       <c r="AO44" s="1"/>
       <c r="AP44" s="1"/>
       <c r="AQ44" s="1"/>
@@ -6373,14 +6486,14 @@
         <v>565</v>
       </c>
       <c r="L45" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-565</v>
       </c>
       <c r="M45" s="1"/>
       <c r="N45" s="1"/>
       <c r="O45" s="1"/>
       <c r="P45" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Q45" s="5">
@@ -6390,17 +6503,17 @@
         <v>500</v>
       </c>
       <c r="S45" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>576</v>
       </c>
       <c r="T45" s="1" t="e">
-        <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U45" s="1" t="e">
         <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="U45" s="1" t="e">
+        <f t="shared" si="20"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="V45" s="1">
         <v>12.4</v>
       </c>
@@ -6435,18 +6548,18 @@
         <v>178</v>
       </c>
       <c r="AG45" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>200</v>
       </c>
       <c r="AH45" s="7">
         <v>16</v>
       </c>
       <c r="AI45" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>36</v>
       </c>
       <c r="AJ45" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>230.4</v>
       </c>
       <c r="AK45" s="1">
@@ -6456,10 +6569,13 @@
         <v>84</v>
       </c>
       <c r="AM45" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.42857142857142855</v>
       </c>
-      <c r="AN45" s="1"/>
+      <c r="AN45" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AO45" s="1"/>
       <c r="AP45" s="1"/>
       <c r="AQ45" s="1"/>
@@ -6503,14 +6619,14 @@
         <v>708</v>
       </c>
       <c r="L46" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-2</v>
       </c>
       <c r="M46" s="1"/>
       <c r="N46" s="1"/>
       <c r="O46" s="1"/>
       <c r="P46" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>141.19999999999999</v>
       </c>
       <c r="Q46" s="5">
@@ -6521,15 +6637,15 @@
         <v>1034.2399999999998</v>
       </c>
       <c r="S46" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1080</v>
       </c>
       <c r="T46" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>15.524079320113316</v>
       </c>
       <c r="U46" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>7.8753541076487261</v>
       </c>
       <c r="V46" s="1">
@@ -6564,18 +6680,18 @@
       </c>
       <c r="AF46" s="1"/>
       <c r="AG46" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>723.96799999999985</v>
       </c>
       <c r="AH46" s="7">
         <v>10</v>
       </c>
       <c r="AI46" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>108</v>
       </c>
       <c r="AJ46" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>756</v>
       </c>
       <c r="AK46" s="1">
@@ -6585,10 +6701,13 @@
         <v>84</v>
       </c>
       <c r="AM46" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1.2857142857142858</v>
       </c>
-      <c r="AN46" s="1"/>
+      <c r="AN46" s="1">
+        <f t="shared" si="6"/>
+        <v>98.839999999999989</v>
+      </c>
       <c r="AO46" s="1"/>
       <c r="AP46" s="1"/>
       <c r="AQ46" s="1"/>
@@ -6632,30 +6751,30 @@
         <v>398</v>
       </c>
       <c r="L47" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-97</v>
       </c>
       <c r="M47" s="1"/>
       <c r="N47" s="1"/>
       <c r="O47" s="1"/>
       <c r="P47" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>60.2</v>
       </c>
       <c r="Q47" s="5"/>
       <c r="R47" s="5"/>
       <c r="S47" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="T47" s="1">
-        <f t="shared" si="18"/>
-        <v>18.704318936877076</v>
-      </c>
-      <c r="U47" s="1">
         <f t="shared" si="19"/>
         <v>18.704318936877076</v>
       </c>
+      <c r="U47" s="1">
+        <f t="shared" si="20"/>
+        <v>18.704318936877076</v>
+      </c>
       <c r="V47" s="1">
         <v>145.6</v>
       </c>
@@ -6688,20 +6807,20 @@
       </c>
       <c r="AF47" s="1"/>
       <c r="AG47" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AH47" s="7">
         <v>16</v>
       </c>
       <c r="AI47" s="9">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AJ47" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
+      <c r="AJ47" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AK47" s="1">
         <v>12</v>
       </c>
@@ -6709,10 +6828,13 @@
         <v>84</v>
       </c>
       <c r="AM47" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AN47" s="1"/>
+      <c r="AN47" s="1">
+        <f t="shared" si="6"/>
+        <v>24.080000000000002</v>
+      </c>
       <c r="AO47" s="1"/>
       <c r="AP47" s="1"/>
       <c r="AQ47" s="1"/>
@@ -6756,14 +6878,14 @@
         <v>939</v>
       </c>
       <c r="L48" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2</v>
       </c>
       <c r="M48" s="1"/>
       <c r="N48" s="1"/>
       <c r="O48" s="1"/>
       <c r="P48" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>188.2</v>
       </c>
       <c r="Q48" s="5">
@@ -6774,15 +6896,15 @@
         <v>1626.6399999999996</v>
       </c>
       <c r="S48" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1680</v>
       </c>
       <c r="T48" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>15.483528161530288</v>
       </c>
       <c r="U48" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>6.5568544102019128</v>
       </c>
       <c r="V48" s="1">
@@ -6817,18 +6939,18 @@
       </c>
       <c r="AF48" s="1"/>
       <c r="AG48" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1138.6479999999997</v>
       </c>
       <c r="AH48" s="7">
         <v>10</v>
       </c>
       <c r="AI48" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>168</v>
       </c>
       <c r="AJ48" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1176</v>
       </c>
       <c r="AK48" s="1">
@@ -6838,10 +6960,13 @@
         <v>84</v>
       </c>
       <c r="AM48" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>2</v>
       </c>
-      <c r="AN48" s="1"/>
+      <c r="AN48" s="1">
+        <f t="shared" si="6"/>
+        <v>131.73999999999998</v>
+      </c>
       <c r="AO48" s="1"/>
       <c r="AP48" s="1"/>
       <c r="AQ48" s="1"/>
@@ -6885,14 +7010,14 @@
         <v>219</v>
       </c>
       <c r="L49" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-20</v>
       </c>
       <c r="M49" s="1"/>
       <c r="N49" s="1"/>
       <c r="O49" s="1"/>
       <c r="P49" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>39.799999999999997</v>
       </c>
       <c r="Q49" s="5">
@@ -6903,15 +7028,15 @@
         <v>395.59999999999997</v>
       </c>
       <c r="S49" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>360</v>
       </c>
       <c r="T49" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>11.105527638190956</v>
       </c>
       <c r="U49" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>2.0603015075376887</v>
       </c>
       <c r="V49" s="1">
@@ -6946,18 +7071,18 @@
       </c>
       <c r="AF49" s="1"/>
       <c r="AG49" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>276.91999999999996</v>
       </c>
       <c r="AH49" s="7">
         <v>10</v>
       </c>
       <c r="AI49" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>36</v>
       </c>
       <c r="AJ49" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>251.99999999999997</v>
       </c>
       <c r="AK49" s="1">
@@ -6967,10 +7092,13 @@
         <v>84</v>
       </c>
       <c r="AM49" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.42857142857142855</v>
       </c>
-      <c r="AN49" s="1"/>
+      <c r="AN49" s="1">
+        <f t="shared" si="6"/>
+        <v>27.859999999999996</v>
+      </c>
       <c r="AO49" s="1"/>
       <c r="AP49" s="1"/>
       <c r="AQ49" s="1"/>
@@ -7014,33 +7142,33 @@
         <v>106</v>
       </c>
       <c r="L50" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-24</v>
       </c>
       <c r="M50" s="1"/>
       <c r="N50" s="1"/>
       <c r="O50" s="1"/>
       <c r="P50" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>16.399999999999999</v>
       </c>
       <c r="Q50" s="5">
         <v>70.599999999999966</v>
       </c>
       <c r="R50" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>70.599999999999966</v>
       </c>
       <c r="S50" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>96</v>
       </c>
       <c r="T50" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>15.54878048780488</v>
       </c>
       <c r="U50" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>9.6951219512195124</v>
       </c>
       <c r="V50" s="1">
@@ -7075,18 +7203,18 @@
       </c>
       <c r="AF50" s="1"/>
       <c r="AG50" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>56.479999999999976</v>
       </c>
       <c r="AH50" s="7">
         <v>8</v>
       </c>
       <c r="AI50" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>12</v>
       </c>
       <c r="AJ50" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>76.800000000000011</v>
       </c>
       <c r="AK50" s="1">
@@ -7096,10 +7224,13 @@
         <v>84</v>
       </c>
       <c r="AM50" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.14285714285714285</v>
       </c>
-      <c r="AN50" s="1"/>
+      <c r="AN50" s="1">
+        <f t="shared" si="6"/>
+        <v>13.12</v>
+      </c>
       <c r="AO50" s="1"/>
       <c r="AP50" s="1"/>
       <c r="AQ50" s="1"/>
@@ -7143,33 +7274,33 @@
         <v>182</v>
       </c>
       <c r="L51" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>5</v>
       </c>
       <c r="M51" s="1"/>
       <c r="N51" s="1"/>
       <c r="O51" s="1"/>
       <c r="P51" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>37.4</v>
       </c>
       <c r="Q51" s="5">
         <v>358.6</v>
       </c>
       <c r="R51" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>358.6</v>
       </c>
       <c r="S51" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>360</v>
       </c>
       <c r="T51" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>14.037433155080214</v>
       </c>
       <c r="U51" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4.4117647058823533</v>
       </c>
       <c r="V51" s="1">
@@ -7204,18 +7335,18 @@
       </c>
       <c r="AF51" s="1"/>
       <c r="AG51" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>358.6</v>
       </c>
       <c r="AH51" s="7">
         <v>5</v>
       </c>
       <c r="AI51" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>72</v>
       </c>
       <c r="AJ51" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>360</v>
       </c>
       <c r="AK51" s="1">
@@ -7225,10 +7356,13 @@
         <v>84</v>
       </c>
       <c r="AM51" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.8571428571428571</v>
       </c>
-      <c r="AN51" s="1"/>
+      <c r="AN51" s="1">
+        <f t="shared" si="6"/>
+        <v>37.4</v>
+      </c>
       <c r="AO51" s="1"/>
       <c r="AP51" s="1"/>
       <c r="AQ51" s="1"/>
@@ -7272,33 +7406,33 @@
         <v>74</v>
       </c>
       <c r="L52" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-4</v>
       </c>
       <c r="M52" s="1"/>
       <c r="N52" s="1"/>
       <c r="O52" s="1"/>
       <c r="P52" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>14</v>
       </c>
       <c r="Q52" s="5">
         <v>58</v>
       </c>
       <c r="R52" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>58</v>
       </c>
       <c r="S52" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>96</v>
       </c>
       <c r="T52" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>16.714285714285715</v>
       </c>
       <c r="U52" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>9.8571428571428577</v>
       </c>
       <c r="V52" s="1">
@@ -7333,18 +7467,18 @@
       </c>
       <c r="AF52" s="1"/>
       <c r="AG52" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>52.2</v>
       </c>
       <c r="AH52" s="7">
         <v>8</v>
       </c>
       <c r="AI52" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>12</v>
       </c>
       <c r="AJ52" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>86.4</v>
       </c>
       <c r="AK52" s="1">
@@ -7354,10 +7488,13 @@
         <v>84</v>
       </c>
       <c r="AM52" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.14285714285714285</v>
       </c>
-      <c r="AN52" s="1"/>
+      <c r="AN52" s="1">
+        <f t="shared" si="6"/>
+        <v>12.6</v>
+      </c>
       <c r="AO52" s="1"/>
       <c r="AP52" s="1"/>
       <c r="AQ52" s="1"/>
@@ -7401,14 +7538,14 @@
         <v>46</v>
       </c>
       <c r="L53" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-6</v>
       </c>
       <c r="M53" s="1"/>
       <c r="N53" s="1"/>
       <c r="O53" s="1"/>
       <c r="P53" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>8</v>
       </c>
       <c r="Q53" s="5"/>
@@ -7417,17 +7554,17 @@
         <v>11.6</v>
       </c>
       <c r="S53" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="T53" s="1">
-        <f t="shared" si="18"/>
-        <v>13.75</v>
-      </c>
-      <c r="U53" s="1">
         <f t="shared" si="19"/>
         <v>13.75</v>
       </c>
+      <c r="U53" s="1">
+        <f t="shared" si="20"/>
+        <v>13.75</v>
+      </c>
       <c r="V53" s="1">
         <v>11.8</v>
       </c>
@@ -7460,20 +7597,20 @@
       </c>
       <c r="AF53" s="1"/>
       <c r="AG53" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>10.44</v>
       </c>
       <c r="AH53" s="7">
         <v>8</v>
       </c>
       <c r="AI53" s="9">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AJ53" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
+      <c r="AJ53" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AK53" s="1">
         <v>12</v>
       </c>
@@ -7481,10 +7618,13 @@
         <v>84</v>
       </c>
       <c r="AM53" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AN53" s="1"/>
+      <c r="AN53" s="1">
+        <f t="shared" si="6"/>
+        <v>7.2</v>
+      </c>
       <c r="AO53" s="1"/>
       <c r="AP53" s="1"/>
       <c r="AQ53" s="1"/>
@@ -7528,30 +7668,30 @@
         <v>275</v>
       </c>
       <c r="L54" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-180</v>
       </c>
       <c r="M54" s="1"/>
       <c r="N54" s="1"/>
       <c r="O54" s="1"/>
       <c r="P54" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>19</v>
       </c>
       <c r="Q54" s="5"/>
       <c r="R54" s="5"/>
       <c r="S54" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="T54" s="1">
-        <f t="shared" si="18"/>
-        <v>31.05263157894737</v>
-      </c>
-      <c r="U54" s="1">
         <f t="shared" si="19"/>
         <v>31.05263157894737</v>
       </c>
+      <c r="U54" s="1">
+        <f t="shared" si="20"/>
+        <v>31.05263157894737</v>
+      </c>
       <c r="V54" s="1">
         <v>37</v>
       </c>
@@ -7584,20 +7724,20 @@
       </c>
       <c r="AF54" s="1"/>
       <c r="AG54" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AH54" s="7">
         <v>5</v>
       </c>
       <c r="AI54" s="9">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AJ54" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
+      <c r="AJ54" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AK54" s="1">
         <v>12</v>
       </c>
@@ -7605,10 +7745,13 @@
         <v>144</v>
       </c>
       <c r="AM54" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AN54" s="1"/>
+      <c r="AN54" s="1">
+        <f t="shared" si="6"/>
+        <v>19</v>
+      </c>
       <c r="AO54" s="1"/>
       <c r="AP54" s="1"/>
       <c r="AQ54" s="1"/>
@@ -7652,14 +7795,14 @@
         <v>149</v>
       </c>
       <c r="L55" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-81</v>
       </c>
       <c r="M55" s="1"/>
       <c r="N55" s="1"/>
       <c r="O55" s="1"/>
       <c r="P55" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>13.6</v>
       </c>
       <c r="Q55" s="5">
@@ -7670,15 +7813,15 @@
         <v>132</v>
       </c>
       <c r="S55" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>120</v>
       </c>
       <c r="T55" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>9.117647058823529</v>
       </c>
       <c r="U55" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.29411764705882354</v>
       </c>
       <c r="V55" s="1">
@@ -7713,18 +7856,18 @@
       </c>
       <c r="AF55" s="1"/>
       <c r="AG55" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>132</v>
       </c>
       <c r="AH55" s="7">
         <v>5</v>
       </c>
       <c r="AI55" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>24</v>
       </c>
       <c r="AJ55" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>120</v>
       </c>
       <c r="AK55" s="1">
@@ -7734,10 +7877,13 @@
         <v>84</v>
       </c>
       <c r="AM55" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.2857142857142857</v>
       </c>
-      <c r="AN55" s="1"/>
+      <c r="AN55" s="1">
+        <f t="shared" si="6"/>
+        <v>13.6</v>
+      </c>
       <c r="AO55" s="1"/>
       <c r="AP55" s="1"/>
       <c r="AQ55" s="1"/>
@@ -7780,30 +7926,30 @@
         <v>7.4</v>
       </c>
       <c r="L56" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M56" s="1"/>
       <c r="N56" s="1"/>
       <c r="O56" s="1"/>
       <c r="P56" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1.48</v>
       </c>
       <c r="Q56" s="5"/>
       <c r="R56" s="5"/>
       <c r="S56" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="T56" s="1">
-        <f t="shared" si="18"/>
-        <v>32.5</v>
-      </c>
-      <c r="U56" s="1">
         <f t="shared" si="19"/>
         <v>32.5</v>
       </c>
+      <c r="U56" s="1">
+        <f t="shared" si="20"/>
+        <v>32.5</v>
+      </c>
       <c r="V56" s="1">
         <v>0.74</v>
       </c>
@@ -7838,20 +7984,20 @@
         <v>123</v>
       </c>
       <c r="AG56" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AH56" s="7">
         <v>3.7</v>
       </c>
       <c r="AI56" s="9">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AJ56" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
+      <c r="AJ56" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AK56" s="1">
         <v>14</v>
       </c>
@@ -7859,10 +8005,13 @@
         <v>126</v>
       </c>
       <c r="AM56" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AN56" s="1"/>
+      <c r="AN56" s="1">
+        <f t="shared" si="6"/>
+        <v>1.48</v>
+      </c>
       <c r="AO56" s="1"/>
       <c r="AP56" s="1"/>
       <c r="AQ56" s="1"/>
@@ -7906,14 +8055,14 @@
         <v>67</v>
       </c>
       <c r="L57" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-4</v>
       </c>
       <c r="M57" s="1"/>
       <c r="N57" s="1"/>
       <c r="O57" s="1"/>
       <c r="P57" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>12.6</v>
       </c>
       <c r="Q57" s="5">
@@ -7924,15 +8073,15 @@
         <v>134.4</v>
       </c>
       <c r="S57" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>168</v>
       </c>
       <c r="T57" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>16.666666666666668</v>
       </c>
       <c r="U57" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>3.3333333333333335</v>
       </c>
       <c r="V57" s="1">
@@ -7967,18 +8116,18 @@
       </c>
       <c r="AF57" s="1"/>
       <c r="AG57" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>30.912000000000003</v>
       </c>
       <c r="AH57" s="7">
         <v>6</v>
       </c>
       <c r="AI57" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>28</v>
       </c>
       <c r="AJ57" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>38.64</v>
       </c>
       <c r="AK57" s="1">
@@ -7988,10 +8137,13 @@
         <v>140</v>
       </c>
       <c r="AM57" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.2</v>
       </c>
-      <c r="AN57" s="1"/>
+      <c r="AN57" s="1">
+        <f t="shared" si="6"/>
+        <v>2.8980000000000001</v>
+      </c>
       <c r="AO57" s="1"/>
       <c r="AP57" s="1"/>
       <c r="AQ57" s="1"/>
@@ -8037,14 +8189,14 @@
         <v>608</v>
       </c>
       <c r="L58" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-53</v>
       </c>
       <c r="M58" s="1"/>
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
       <c r="P58" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>111</v>
       </c>
       <c r="Q58" s="5">
@@ -8055,15 +8207,15 @@
         <v>494.2</v>
       </c>
       <c r="S58" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>504</v>
       </c>
       <c r="T58" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>15.288288288288289</v>
       </c>
       <c r="U58" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>10.747747747747749</v>
       </c>
       <c r="V58" s="1">
@@ -8098,18 +8250,18 @@
       </c>
       <c r="AF58" s="1"/>
       <c r="AG58" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>123.55</v>
       </c>
       <c r="AH58" s="7">
         <v>12</v>
       </c>
       <c r="AI58" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>42</v>
       </c>
       <c r="AJ58" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>126</v>
       </c>
       <c r="AK58" s="1">
@@ -8119,10 +8271,13 @@
         <v>70</v>
       </c>
       <c r="AM58" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.6</v>
       </c>
-      <c r="AN58" s="1"/>
+      <c r="AN58" s="1">
+        <f t="shared" si="6"/>
+        <v>27.75</v>
+      </c>
       <c r="AO58" s="1"/>
       <c r="AP58" s="1"/>
       <c r="AQ58" s="1"/>
@@ -8166,14 +8321,14 @@
         <v>414</v>
       </c>
       <c r="L59" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>20</v>
       </c>
       <c r="M59" s="1"/>
       <c r="N59" s="1"/>
       <c r="O59" s="1"/>
       <c r="P59" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>86.8</v>
       </c>
       <c r="Q59" s="5">
@@ -8184,15 +8339,15 @@
         <v>852</v>
       </c>
       <c r="S59" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>840</v>
       </c>
       <c r="T59" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>9.8617511520737331</v>
       </c>
       <c r="U59" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.18433179723502305</v>
       </c>
       <c r="V59" s="1">
@@ -8227,18 +8382,18 @@
       </c>
       <c r="AF59" s="1"/>
       <c r="AG59" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>213</v>
       </c>
       <c r="AH59" s="7">
         <v>12</v>
       </c>
       <c r="AI59" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>70</v>
       </c>
       <c r="AJ59" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>210</v>
       </c>
       <c r="AK59" s="1">
@@ -8248,10 +8403,13 @@
         <v>70</v>
       </c>
       <c r="AM59" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="AN59" s="1"/>
+      <c r="AN59" s="1">
+        <f t="shared" si="6"/>
+        <v>21.7</v>
+      </c>
       <c r="AO59" s="1"/>
       <c r="AP59" s="1"/>
       <c r="AQ59" s="1"/>
@@ -8293,30 +8451,30 @@
         <v>14</v>
       </c>
       <c r="L60" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M60" s="1"/>
       <c r="N60" s="1"/>
       <c r="O60" s="1"/>
       <c r="P60" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2.8</v>
       </c>
       <c r="Q60" s="5"/>
       <c r="R60" s="5"/>
       <c r="S60" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="T60" s="1">
-        <f t="shared" si="18"/>
-        <v>24.642857142857146</v>
-      </c>
-      <c r="U60" s="1">
         <f t="shared" si="19"/>
         <v>24.642857142857146</v>
       </c>
+      <c r="U60" s="1">
+        <f t="shared" si="20"/>
+        <v>24.642857142857146</v>
+      </c>
       <c r="V60" s="1">
         <v>2</v>
       </c>
@@ -8351,20 +8509,20 @@
         <v>123</v>
       </c>
       <c r="AG60" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AH60" s="7">
         <v>6</v>
       </c>
       <c r="AI60" s="9">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AJ60" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
+      <c r="AJ60" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AK60" s="1">
         <v>14</v>
       </c>
@@ -8372,10 +8530,13 @@
         <v>140</v>
       </c>
       <c r="AM60" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AN60" s="1"/>
+      <c r="AN60" s="1">
+        <f t="shared" si="6"/>
+        <v>0.504</v>
+      </c>
       <c r="AO60" s="1"/>
       <c r="AP60" s="1"/>
       <c r="AQ60" s="1"/>
@@ -8419,14 +8580,14 @@
         <v>15</v>
       </c>
       <c r="L61" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M61" s="1"/>
       <c r="N61" s="1"/>
       <c r="O61" s="1"/>
       <c r="P61" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3</v>
       </c>
       <c r="Q61" s="5"/>
@@ -8435,17 +8596,17 @@
         <v>15.6</v>
       </c>
       <c r="S61" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="T61" s="1">
-        <f t="shared" si="18"/>
-        <v>10</v>
-      </c>
-      <c r="U61" s="1">
         <f t="shared" si="19"/>
         <v>10</v>
       </c>
+      <c r="U61" s="1">
+        <f t="shared" si="20"/>
+        <v>10</v>
+      </c>
       <c r="V61" s="1">
         <v>0.8</v>
       </c>
@@ -8478,20 +8639,20 @@
       </c>
       <c r="AF61" s="1"/>
       <c r="AG61" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2.8079999999999998</v>
       </c>
       <c r="AH61" s="7">
         <v>6</v>
       </c>
       <c r="AI61" s="9">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AJ61" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
+      <c r="AJ61" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AK61" s="1">
         <v>14</v>
       </c>
@@ -8499,10 +8660,13 @@
         <v>140</v>
       </c>
       <c r="AM61" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AN61" s="1"/>
+      <c r="AN61" s="1">
+        <f t="shared" si="6"/>
+        <v>0.54</v>
+      </c>
       <c r="AO61" s="1"/>
       <c r="AP61" s="1"/>
       <c r="AQ61" s="1"/>
@@ -8544,30 +8708,30 @@
         <v>12</v>
       </c>
       <c r="L62" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M62" s="1"/>
       <c r="N62" s="1"/>
       <c r="O62" s="1"/>
       <c r="P62" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2.4</v>
       </c>
       <c r="Q62" s="5"/>
       <c r="R62" s="5"/>
       <c r="S62" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="T62" s="1">
-        <f t="shared" si="18"/>
-        <v>16.25</v>
-      </c>
-      <c r="U62" s="1">
         <f t="shared" si="19"/>
         <v>16.25</v>
       </c>
+      <c r="U62" s="1">
+        <f t="shared" si="20"/>
+        <v>16.25</v>
+      </c>
       <c r="V62" s="1">
         <v>1.2</v>
       </c>
@@ -8600,20 +8764,20 @@
       </c>
       <c r="AF62" s="1"/>
       <c r="AG62" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AH62" s="7">
         <v>6</v>
       </c>
       <c r="AI62" s="9">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AJ62" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
+      <c r="AJ62" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AK62" s="1">
         <v>14</v>
       </c>
@@ -8621,10 +8785,13 @@
         <v>140</v>
       </c>
       <c r="AM62" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AN62" s="1"/>
+      <c r="AN62" s="1">
+        <f t="shared" si="6"/>
+        <v>0.432</v>
+      </c>
       <c r="AO62" s="1"/>
       <c r="AP62" s="1"/>
       <c r="AQ62" s="1"/>
@@ -8668,33 +8835,33 @@
         <v>529</v>
       </c>
       <c r="L63" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-2</v>
       </c>
       <c r="M63" s="1"/>
       <c r="N63" s="1"/>
       <c r="O63" s="1"/>
       <c r="P63" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>105.4</v>
       </c>
       <c r="Q63" s="5">
         <v>1077.6000000000001</v>
       </c>
       <c r="R63" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1077.6000000000001</v>
       </c>
       <c r="S63" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1008</v>
       </c>
       <c r="T63" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>13.339658444022771</v>
       </c>
       <c r="U63" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>3.7760910815939277</v>
       </c>
       <c r="V63" s="1">
@@ -8729,18 +8896,18 @@
       </c>
       <c r="AF63" s="1"/>
       <c r="AG63" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>323.28000000000003</v>
       </c>
       <c r="AH63" s="7">
         <v>12</v>
       </c>
       <c r="AI63" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>84</v>
       </c>
       <c r="AJ63" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>302.39999999999998</v>
       </c>
       <c r="AK63" s="1">
@@ -8750,10 +8917,13 @@
         <v>70</v>
       </c>
       <c r="AM63" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1.2</v>
       </c>
-      <c r="AN63" s="1"/>
+      <c r="AN63" s="1">
+        <f t="shared" si="6"/>
+        <v>31.62</v>
+      </c>
       <c r="AO63" s="1"/>
       <c r="AP63" s="1"/>
       <c r="AQ63" s="1"/>
@@ -8797,33 +8967,33 @@
         <v>403</v>
       </c>
       <c r="L64" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-21</v>
       </c>
       <c r="M64" s="1"/>
       <c r="N64" s="1"/>
       <c r="O64" s="1"/>
       <c r="P64" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>76.400000000000006</v>
       </c>
       <c r="Q64" s="5">
         <v>364.60000000000014</v>
       </c>
       <c r="R64" s="5">
-        <f t="shared" ref="R64:R65" si="21">IF(14*P64-F64+P64*$R$1&lt;0,0,14*P64-F64+P64*$R$1)</f>
+        <f t="shared" ref="R64:R65" si="22">IF(14*P64-F64+P64*$R$1&lt;0,0,14*P64-F64+P64*$R$1)</f>
         <v>456.28000000000014</v>
       </c>
       <c r="S64" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>504</v>
       </c>
       <c r="T64" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>15.82460732984293</v>
       </c>
       <c r="U64" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>9.2277486910994764</v>
       </c>
       <c r="V64" s="1">
@@ -8858,18 +9028,18 @@
       </c>
       <c r="AF64" s="1"/>
       <c r="AG64" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>136.88400000000004</v>
       </c>
       <c r="AH64" s="7">
         <v>12</v>
       </c>
       <c r="AI64" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>42</v>
       </c>
       <c r="AJ64" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>151.19999999999999</v>
       </c>
       <c r="AK64" s="1">
@@ -8879,10 +9049,13 @@
         <v>70</v>
       </c>
       <c r="AM64" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.6</v>
       </c>
-      <c r="AN64" s="1"/>
+      <c r="AN64" s="1">
+        <f t="shared" si="6"/>
+        <v>22.92</v>
+      </c>
       <c r="AO64" s="1"/>
       <c r="AP64" s="1"/>
       <c r="AQ64" s="1"/>
@@ -8926,33 +9099,33 @@
         <v>190</v>
       </c>
       <c r="L65" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="M65" s="1"/>
       <c r="N65" s="1"/>
       <c r="O65" s="1"/>
       <c r="P65" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>38.200000000000003</v>
       </c>
       <c r="Q65" s="5"/>
       <c r="R65" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>32.640000000000072</v>
       </c>
       <c r="S65" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="T65" s="1">
-        <f t="shared" si="18"/>
-        <v>14.345549738219894</v>
-      </c>
-      <c r="U65" s="1">
         <f t="shared" si="19"/>
         <v>14.345549738219894</v>
       </c>
+      <c r="U65" s="1">
+        <f t="shared" si="20"/>
+        <v>14.345549738219894</v>
+      </c>
       <c r="V65" s="1">
         <v>31.2</v>
       </c>
@@ -8985,20 +9158,20 @@
       </c>
       <c r="AF65" s="1"/>
       <c r="AG65" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>9.7920000000000211</v>
       </c>
       <c r="AH65" s="7">
         <v>14</v>
       </c>
       <c r="AI65" s="9">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AJ65" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
+      <c r="AJ65" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AK65" s="1">
         <v>14</v>
       </c>
@@ -9006,10 +9179,13 @@
         <v>70</v>
       </c>
       <c r="AM65" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AN65" s="1"/>
+      <c r="AN65" s="1">
+        <f t="shared" si="6"/>
+        <v>11.46</v>
+      </c>
       <c r="AO65" s="1"/>
       <c r="AP65" s="1"/>
       <c r="AQ65" s="1"/>
@@ -9051,14 +9227,14 @@
         <v>222</v>
       </c>
       <c r="L66" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-39</v>
       </c>
       <c r="M66" s="1"/>
       <c r="N66" s="1"/>
       <c r="O66" s="1"/>
       <c r="P66" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>36.6</v>
       </c>
       <c r="Q66" s="5">
@@ -9069,15 +9245,15 @@
         <v>362</v>
       </c>
       <c r="S66" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>336</v>
       </c>
       <c r="T66" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>9.2896174863387966</v>
       </c>
       <c r="U66" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.10928961748633879</v>
       </c>
       <c r="V66" s="1">
@@ -9114,18 +9290,18 @@
         <v>164</v>
       </c>
       <c r="AG66" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>79.64</v>
       </c>
       <c r="AH66" s="7">
         <v>6</v>
       </c>
       <c r="AI66" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>56</v>
       </c>
       <c r="AJ66" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>73.92</v>
       </c>
       <c r="AK66" s="1">
@@ -9135,10 +9311,13 @@
         <v>140</v>
       </c>
       <c r="AM66" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.4</v>
       </c>
-      <c r="AN66" s="1"/>
+      <c r="AN66" s="1">
+        <f t="shared" si="6"/>
+        <v>8.0519999999999996</v>
+      </c>
       <c r="AO66" s="1"/>
       <c r="AP66" s="1"/>
       <c r="AQ66" s="1"/>
@@ -9182,33 +9361,33 @@
         <v>851</v>
       </c>
       <c r="L67" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-46</v>
       </c>
       <c r="M67" s="1"/>
       <c r="N67" s="1"/>
       <c r="O67" s="1"/>
       <c r="P67" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>161</v>
       </c>
       <c r="Q67" s="5">
         <v>824</v>
       </c>
       <c r="R67" s="5">
-        <f t="shared" ref="R67:R69" si="22">IF(14*P67-F67+P67*$R$1&lt;0,0,14*P67-F67+P67*$R$1)</f>
+        <f t="shared" ref="R67:R69" si="23">IF(14*P67-F67+P67*$R$1&lt;0,0,14*P67-F67+P67*$R$1)</f>
         <v>1017.2</v>
       </c>
       <c r="S67" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1008</v>
       </c>
       <c r="T67" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>15.142857142857142</v>
       </c>
       <c r="U67" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>8.8819875776397517</v>
       </c>
       <c r="V67" s="1">
@@ -9243,18 +9422,18 @@
       </c>
       <c r="AF67" s="1"/>
       <c r="AG67" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>254.3</v>
       </c>
       <c r="AH67" s="7">
         <v>12</v>
       </c>
       <c r="AI67" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>84</v>
       </c>
       <c r="AJ67" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>252</v>
       </c>
       <c r="AK67" s="1">
@@ -9264,10 +9443,13 @@
         <v>70</v>
       </c>
       <c r="AM67" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1.2</v>
       </c>
-      <c r="AN67" s="1"/>
+      <c r="AN67" s="1">
+        <f t="shared" si="6"/>
+        <v>40.25</v>
+      </c>
       <c r="AO67" s="1"/>
       <c r="AP67" s="1"/>
       <c r="AQ67" s="1"/>
@@ -9311,33 +9493,33 @@
         <v>740</v>
       </c>
       <c r="L68" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M68" s="1"/>
       <c r="N68" s="1"/>
       <c r="O68" s="1"/>
       <c r="P68" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>148</v>
       </c>
       <c r="Q68" s="5">
         <v>1012</v>
       </c>
       <c r="R68" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1189.5999999999999</v>
       </c>
       <c r="S68" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1176</v>
       </c>
       <c r="T68" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>15.108108108108109</v>
       </c>
       <c r="U68" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>7.1621621621621623</v>
       </c>
       <c r="V68" s="1">
@@ -9372,18 +9554,18 @@
       </c>
       <c r="AF68" s="1"/>
       <c r="AG68" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>297.39999999999998</v>
       </c>
       <c r="AH68" s="7">
         <v>12</v>
       </c>
       <c r="AI68" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>98</v>
       </c>
       <c r="AJ68" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>294</v>
       </c>
       <c r="AK68" s="1">
@@ -9393,10 +9575,13 @@
         <v>70</v>
       </c>
       <c r="AM68" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1.4</v>
       </c>
-      <c r="AN68" s="1"/>
+      <c r="AN68" s="1">
+        <f t="shared" si="6"/>
+        <v>37</v>
+      </c>
       <c r="AO68" s="1"/>
       <c r="AP68" s="1"/>
       <c r="AQ68" s="1"/>
@@ -9440,33 +9625,33 @@
         <v>93</v>
       </c>
       <c r="L69" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-5</v>
       </c>
       <c r="M69" s="1"/>
       <c r="N69" s="1"/>
       <c r="O69" s="1"/>
       <c r="P69" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>17.600000000000001</v>
       </c>
       <c r="Q69" s="5">
         <v>90.400000000000034</v>
       </c>
       <c r="R69" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>111.52000000000004</v>
       </c>
       <c r="S69" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>84</v>
       </c>
       <c r="T69" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>13.636363636363635</v>
       </c>
       <c r="U69" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>8.8636363636363633</v>
       </c>
       <c r="V69" s="1">
@@ -9501,18 +9686,18 @@
       </c>
       <c r="AF69" s="1"/>
       <c r="AG69" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>22.304000000000009</v>
       </c>
       <c r="AH69" s="7">
         <v>6</v>
       </c>
       <c r="AI69" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>14</v>
       </c>
       <c r="AJ69" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>16.8</v>
       </c>
       <c r="AK69" s="1">
@@ -9522,10 +9707,13 @@
         <v>140</v>
       </c>
       <c r="AM69" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.1</v>
       </c>
-      <c r="AN69" s="1"/>
+      <c r="AN69" s="1">
+        <f t="shared" si="6"/>
+        <v>3.5200000000000005</v>
+      </c>
       <c r="AO69" s="1"/>
       <c r="AP69" s="1"/>
       <c r="AQ69" s="1"/>
@@ -9569,14 +9757,14 @@
         <v>155</v>
       </c>
       <c r="L70" s="1">
-        <f t="shared" ref="L70:L73" si="23">E70-K70</f>
+        <f t="shared" ref="L70:L73" si="24">E70-K70</f>
         <v>-3</v>
       </c>
       <c r="M70" s="1"/>
       <c r="N70" s="1"/>
       <c r="O70" s="1"/>
       <c r="P70" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>30.4</v>
       </c>
       <c r="Q70" s="5">
@@ -9587,15 +9775,15 @@
         <v>293.2</v>
       </c>
       <c r="S70" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>252</v>
       </c>
       <c r="T70" s="1">
-        <f t="shared" ref="T70:T73" si="24">(F70+S70)/P70</f>
+        <f t="shared" ref="T70:T73" si="25">(F70+S70)/P70</f>
         <v>11.644736842105264</v>
       </c>
       <c r="U70" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>3.3552631578947372</v>
       </c>
       <c r="V70" s="1">
@@ -9630,18 +9818,18 @@
       </c>
       <c r="AF70" s="1"/>
       <c r="AG70" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>67.436000000000007</v>
       </c>
       <c r="AH70" s="7">
         <v>6</v>
       </c>
       <c r="AI70" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>42</v>
       </c>
       <c r="AJ70" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>57.96</v>
       </c>
       <c r="AK70" s="1">
@@ -9651,10 +9839,13 @@
         <v>140</v>
       </c>
       <c r="AM70" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.3</v>
       </c>
-      <c r="AN70" s="1"/>
+      <c r="AN70" s="1">
+        <f t="shared" si="6"/>
+        <v>6.992</v>
+      </c>
       <c r="AO70" s="1"/>
       <c r="AP70" s="1"/>
       <c r="AQ70" s="1"/>
@@ -9696,14 +9887,14 @@
         <v>397</v>
       </c>
       <c r="L71" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-36</v>
       </c>
       <c r="M71" s="1"/>
       <c r="N71" s="1"/>
       <c r="O71" s="1"/>
       <c r="P71" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>72.2</v>
       </c>
       <c r="Q71" s="5">
@@ -9714,15 +9905,15 @@
         <v>709.2</v>
       </c>
       <c r="S71" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>672</v>
       </c>
       <c r="T71" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>10.484764542936288</v>
       </c>
       <c r="U71" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1.1772853185595566</v>
       </c>
       <c r="V71" s="1">
@@ -9759,18 +9950,18 @@
         <v>164</v>
       </c>
       <c r="AG71" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>163.11600000000001</v>
       </c>
       <c r="AH71" s="7">
         <v>6</v>
       </c>
       <c r="AI71" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>112</v>
       </c>
       <c r="AJ71" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>154.56</v>
       </c>
       <c r="AK71" s="1">
@@ -9780,10 +9971,13 @@
         <v>140</v>
       </c>
       <c r="AM71" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.8</v>
       </c>
-      <c r="AN71" s="1"/>
+      <c r="AN71" s="1">
+        <f t="shared" ref="AN71:AN73" si="26">P71*G71</f>
+        <v>16.606000000000002</v>
+      </c>
       <c r="AO71" s="1"/>
       <c r="AP71" s="1"/>
       <c r="AQ71" s="1"/>
@@ -9827,28 +10021,28 @@
         <v>18.899999999999999</v>
       </c>
       <c r="L72" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="M72" s="1"/>
       <c r="N72" s="1"/>
       <c r="O72" s="1"/>
       <c r="P72" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3.78</v>
       </c>
       <c r="Q72" s="5"/>
       <c r="R72" s="5"/>
       <c r="S72" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="T72" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>20</v>
       </c>
       <c r="U72" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="V72" s="1">
@@ -9883,20 +10077,20 @@
       </c>
       <c r="AF72" s="1"/>
       <c r="AG72" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AH72" s="7">
         <v>2.7</v>
       </c>
       <c r="AI72" s="9">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AJ72" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
+      <c r="AJ72" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="AK72" s="1">
         <v>14</v>
       </c>
@@ -9904,10 +10098,13 @@
         <v>126</v>
       </c>
       <c r="AM72" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AN72" s="1"/>
+      <c r="AN72" s="1">
+        <f t="shared" si="26"/>
+        <v>3.78</v>
+      </c>
       <c r="AO72" s="1"/>
       <c r="AP72" s="1"/>
       <c r="AQ72" s="1"/>
@@ -9951,14 +10148,14 @@
         <v>340</v>
       </c>
       <c r="L73" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-20</v>
       </c>
       <c r="M73" s="1"/>
       <c r="N73" s="1"/>
       <c r="O73" s="1"/>
       <c r="P73" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>64</v>
       </c>
       <c r="Q73" s="5">
@@ -9969,15 +10166,15 @@
         <v>402.8</v>
       </c>
       <c r="S73" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>420</v>
       </c>
       <c r="T73" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>15.46875</v>
       </c>
       <c r="U73" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>8.90625</v>
       </c>
       <c r="V73" s="1">
@@ -10012,18 +10209,18 @@
       </c>
       <c r="AF73" s="1"/>
       <c r="AG73" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>402.8</v>
       </c>
       <c r="AH73" s="7">
         <v>5</v>
       </c>
       <c r="AI73" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>84</v>
       </c>
       <c r="AJ73" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>420</v>
       </c>
       <c r="AK73" s="1">
@@ -10033,10 +10230,13 @@
         <v>84</v>
       </c>
       <c r="AM73" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="AN73" s="1"/>
+      <c r="AN73" s="1">
+        <f t="shared" si="26"/>
+        <v>64</v>
+      </c>
       <c r="AO73" s="1"/>
       <c r="AP73" s="1"/>
       <c r="AQ73" s="1"/>
